--- a/artfynd/A 26749-2026 artfynd.xlsx
+++ b/artfynd/A 26749-2026 artfynd.xlsx
@@ -1526,7 +1526,7 @@
         <v>134232888</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26749-2026 artfynd.xlsx
+++ b/artfynd/A 26749-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131282243</v>
+        <v>134232888</v>
       </c>
       <c r="B2" t="n">
-        <v>99044</v>
+        <v>79130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520006</v>
+        <v>519959</v>
       </c>
       <c r="R2" t="n">
-        <v>6875735</v>
+        <v>6875828</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131282239</v>
+        <v>131282245</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520154</v>
+        <v>520038</v>
       </c>
       <c r="R3" t="n">
-        <v>6875542</v>
+        <v>6875563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131282246</v>
+        <v>125221176</v>
       </c>
       <c r="B4" t="n">
-        <v>99044</v>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -920,16 +930,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520034</v>
+        <v>520250</v>
       </c>
       <c r="R4" t="n">
-        <v>6875561</v>
+        <v>6875499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131282240</v>
+        <v>131282239</v>
       </c>
       <c r="B5" t="n">
-        <v>99044</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,14 +1043,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kårböle, Hls</t>
+          <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519987</v>
+        <v>520154</v>
       </c>
       <c r="R5" t="n">
-        <v>6875451</v>
+        <v>6875542</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131282244</v>
+        <v>131282240</v>
       </c>
       <c r="B6" t="n">
-        <v>99044</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,14 +1149,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finneby, Hls</t>
+          <t>Kårböle, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520069</v>
+        <v>519987</v>
       </c>
       <c r="R6" t="n">
-        <v>6875688</v>
+        <v>6875451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131282242</v>
+        <v>131282241</v>
       </c>
       <c r="B7" t="n">
-        <v>99044</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519963</v>
+        <v>519796</v>
       </c>
       <c r="R7" t="n">
-        <v>6875797</v>
+        <v>6875829</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131282241</v>
+        <v>131282242</v>
       </c>
       <c r="B8" t="n">
-        <v>99044</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519796</v>
+        <v>519963</v>
       </c>
       <c r="R8" t="n">
-        <v>6875829</v>
+        <v>6875797</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131282245</v>
+        <v>131282243</v>
       </c>
       <c r="B9" t="n">
-        <v>98961</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1456,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520038</v>
+        <v>520006</v>
       </c>
       <c r="R9" t="n">
-        <v>6875563</v>
+        <v>6875735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,32 +1538,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134232888</v>
+        <v>131282244</v>
       </c>
       <c r="B10" t="n">
-        <v>79123</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,13 +1577,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519959</v>
+        <v>520069</v>
       </c>
       <c r="R10" t="n">
-        <v>6875828</v>
+        <v>6875688</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,22 +1607,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1636,6 +1641,112 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131282246</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Finneby, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>520034</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6875561</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26749-2026 artfynd.xlsx
+++ b/artfynd/A 26749-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232888</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131282245</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221176</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131282239</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131282240</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131282241</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131282242</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131282243</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131282244</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,8 +1797,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131282246</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>